--- a/DownloadedExcels/distributorProfileBulkUpdate.xlsx
+++ b/DownloadedExcels/distributorProfileBulkUpdate.xlsx
@@ -228,7 +228,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>N02N02N02N02N02</t>
+          <t>N01001001001001001001001</t>
         </is>
       </c>
       <c r="E2" s="4" t="n">

--- a/DownloadedExcels/distributorProfileBulkUpdate.xlsx
+++ b/DownloadedExcels/distributorProfileBulkUpdate.xlsx
@@ -75,6 +75,7 @@
     <col min="9" max="9" style="4" width="8.0" customWidth="false"/>
     <col min="10" max="10" style="4" width="8.0" customWidth="false"/>
     <col min="11" max="11" style="4" width="8.0" customWidth="false"/>
+    <col min="14" max="14" style="1" width="8.0" customWidth="false"/>
     <col min="15" max="15" style="2" width="8.0" customWidth="false"/>
     <col min="18" max="18" style="2" width="8.0" customWidth="false"/>
     <col min="19" max="19" style="2" width="8.0" customWidth="false"/>
@@ -149,7 +150,7 @@
           <t>Auto Inventory Allocation</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Threshold Time For Delivery Date</t>
         </is>
@@ -213,50 +214,48 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>50250327</t>
+          <t>15437620</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MULLER &amp; PHIPPS (KORANGI - KARACHI)</t>
+          <t>M/S. ATLANTIC DISTRIBUTION</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>03001</t>
+          <t>03002</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>N01001001001001001001001</t>
+          <t>002001D05033D10611D33063D95869</t>
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>40.844556</v>
+        <v>60.5351</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>40.844556</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>60.5351</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>4.0</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>40.844556</v>
+        <v>60.5351</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>40.844556</v>
+        <v>60.5351</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>40.844556</v>
+        <v>60.5351</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>40.844556</v>
+        <v>60.5351</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>MON</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -264,9 +263,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>18:18:00</t>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="O2" s="2" t="n">
@@ -274,7 +273,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Estimated RT margin is based on asfrecommended resale prices for calculation purposes only.</t>
+          <t/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -285,36 +284,32 @@
       <c r="R2" s="2" t="n">
         <v>4.0</v>
       </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="S2" s="2" t="n">
+        <v>1.0</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="X2" s="4" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>2000.0</v>
+      </c>
+      <c r="Y2" s="2" t="n">
+        <v>15.0</v>
       </c>
     </row>
   </sheetData>
